--- a/data/nzd0007/nzd0007.xlsx
+++ b/data/nzd0007/nzd0007.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL109"/>
+  <dimension ref="A1:AL110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13037,6 +13037,126 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>305.87</v>
+      </c>
+      <c r="C110" t="n">
+        <v>307.61</v>
+      </c>
+      <c r="D110" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="E110" t="n">
+        <v>314.37</v>
+      </c>
+      <c r="F110" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="G110" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="H110" t="n">
+        <v>355.93</v>
+      </c>
+      <c r="I110" t="n">
+        <v>358.36</v>
+      </c>
+      <c r="J110" t="n">
+        <v>357.54</v>
+      </c>
+      <c r="K110" t="n">
+        <v>360.81</v>
+      </c>
+      <c r="L110" t="n">
+        <v>380.8</v>
+      </c>
+      <c r="M110" t="n">
+        <v>353.05</v>
+      </c>
+      <c r="N110" t="n">
+        <v>345.84</v>
+      </c>
+      <c r="O110" t="n">
+        <v>342.58</v>
+      </c>
+      <c r="P110" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="R110" t="n">
+        <v>324.88</v>
+      </c>
+      <c r="S110" t="n">
+        <v>319.19</v>
+      </c>
+      <c r="T110" t="n">
+        <v>320.41</v>
+      </c>
+      <c r="U110" t="n">
+        <v>319.92</v>
+      </c>
+      <c r="V110" t="n">
+        <v>315.04</v>
+      </c>
+      <c r="W110" t="n">
+        <v>306.3</v>
+      </c>
+      <c r="X110" t="n">
+        <v>298.85</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>296.17</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>287.88</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>279.62</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>277.29</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>279.42</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>278.27</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>273.4</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>281.68</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>292.42</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>306.21</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>325.83</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>327.58</v>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13048,7 +13168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14161,6 +14281,16 @@
       </c>
       <c r="B111" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -14329,28 +14459,28 @@
         <v>0.0633</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05753325497686882</v>
+        <v>-0.06093721531361151</v>
       </c>
       <c r="J2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0009505500623933072</v>
+        <v>0.001084502867483961</v>
       </c>
       <c r="M2" t="n">
-        <v>13.05443307241998</v>
+        <v>12.92662851038778</v>
       </c>
       <c r="N2" t="n">
-        <v>241.4976331240475</v>
+        <v>238.8308034203139</v>
       </c>
       <c r="O2" t="n">
-        <v>15.54019411474797</v>
+        <v>15.45415165644216</v>
       </c>
       <c r="P2" t="n">
-        <v>309.4384701192625</v>
+        <v>309.4695736320803</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14407,28 +14537,28 @@
         <v>0.047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07178052555041457</v>
+        <v>0.07966950473470637</v>
       </c>
       <c r="J3" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001244457696125245</v>
+        <v>0.001556520399431882</v>
       </c>
       <c r="M3" t="n">
-        <v>13.21265068450839</v>
+        <v>13.11846441650753</v>
       </c>
       <c r="N3" t="n">
-        <v>280.453740750368</v>
+        <v>277.5935667022254</v>
       </c>
       <c r="O3" t="n">
-        <v>16.74675314054542</v>
+        <v>16.66113941788572</v>
       </c>
       <c r="P3" t="n">
-        <v>300.8631248489837</v>
+        <v>300.7890128021286</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14485,28 +14615,28 @@
         <v>0.0373</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2008038766665892</v>
+        <v>0.2262507369425404</v>
       </c>
       <c r="J4" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008162216532607625</v>
+        <v>0.01042233854470009</v>
       </c>
       <c r="M4" t="n">
-        <v>14.48655678295321</v>
+        <v>14.51850284873469</v>
       </c>
       <c r="N4" t="n">
-        <v>323.9606386849056</v>
+        <v>322.9467020206804</v>
       </c>
       <c r="O4" t="n">
-        <v>17.99890659692709</v>
+        <v>17.97071790498867</v>
       </c>
       <c r="P4" t="n">
-        <v>296.7898212654445</v>
+        <v>296.5444335142799</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14563,28 +14693,28 @@
         <v>0.0321</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2295851603614054</v>
+        <v>-0.2157597804379667</v>
       </c>
       <c r="J5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0125219934433447</v>
+        <v>0.01123210408229536</v>
       </c>
       <c r="M5" t="n">
-        <v>13.79131945745488</v>
+        <v>13.72198744981922</v>
       </c>
       <c r="N5" t="n">
-        <v>295.6770261416037</v>
+        <v>293.2285948039512</v>
       </c>
       <c r="O5" t="n">
-        <v>17.19526173518751</v>
+        <v>17.12391879226105</v>
       </c>
       <c r="P5" t="n">
-        <v>311.7274912080873</v>
+        <v>311.6042260058646</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14641,28 +14771,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03461898505183951</v>
+        <v>0.05015594929900398</v>
       </c>
       <c r="J6" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000229140573737463</v>
+        <v>0.0004877474267394044</v>
       </c>
       <c r="M6" t="n">
-        <v>14.27541642439005</v>
+        <v>14.22246131922984</v>
       </c>
       <c r="N6" t="n">
-        <v>338.3487278375815</v>
+        <v>335.6278896119471</v>
       </c>
       <c r="O6" t="n">
-        <v>18.39425801269466</v>
+        <v>18.32014982504093</v>
       </c>
       <c r="P6" t="n">
-        <v>330.1074702223683</v>
+        <v>329.9572356189169</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14719,28 +14849,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1094986275777764</v>
+        <v>-0.0939109599202916</v>
       </c>
       <c r="J7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001796333997358124</v>
+        <v>0.001341165290280166</v>
       </c>
       <c r="M7" t="n">
-        <v>16.06875827389444</v>
+        <v>15.96767107380657</v>
       </c>
       <c r="N7" t="n">
-        <v>396.6809640294741</v>
+        <v>393.0891669889938</v>
       </c>
       <c r="O7" t="n">
-        <v>19.91685125790405</v>
+        <v>19.8264764138511</v>
       </c>
       <c r="P7" t="n">
-        <v>349.36922613044</v>
+        <v>349.2063403064984</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14797,28 +14927,28 @@
         <v>0.1955</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1185746913485056</v>
+        <v>0.1298188384521401</v>
       </c>
       <c r="J8" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K8" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002533014824769197</v>
+        <v>0.003083354004021821</v>
       </c>
       <c r="M8" t="n">
-        <v>14.29396126193524</v>
+        <v>14.17736321826898</v>
       </c>
       <c r="N8" t="n">
-        <v>328.5511982066153</v>
+        <v>325.2072394649171</v>
       </c>
       <c r="O8" t="n">
-        <v>18.12598130327336</v>
+        <v>18.03350324992116</v>
       </c>
       <c r="P8" t="n">
-        <v>346.6006298988938</v>
+        <v>346.4831010678326</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14875,28 +15005,28 @@
         <v>0.1138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01777748369891509</v>
+        <v>0.02556703729407084</v>
       </c>
       <c r="J9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L9" t="n">
-        <v>5.073631006136115e-05</v>
+        <v>0.0001067412194142303</v>
       </c>
       <c r="M9" t="n">
-        <v>14.72259940572525</v>
+        <v>14.58813241426916</v>
       </c>
       <c r="N9" t="n">
-        <v>389.6082226978223</v>
+        <v>385.4939362773504</v>
       </c>
       <c r="O9" t="n">
-        <v>19.73849595835058</v>
+        <v>19.63399949774244</v>
       </c>
       <c r="P9" t="n">
-        <v>353.434797377255</v>
+        <v>353.3573873986759</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14953,28 +15083,28 @@
         <v>0.0704</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3510968665570976</v>
+        <v>0.337792815967658</v>
       </c>
       <c r="J10" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K10" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02025252777226683</v>
+        <v>0.01908039632690461</v>
       </c>
       <c r="M10" t="n">
-        <v>16.04773112894044</v>
+        <v>15.9795025103822</v>
       </c>
       <c r="N10" t="n">
-        <v>401.4621318818987</v>
+        <v>397.608218767784</v>
       </c>
       <c r="O10" t="n">
-        <v>20.03651995437079</v>
+        <v>19.94011581630819</v>
       </c>
       <c r="P10" t="n">
-        <v>356.1021400377606</v>
+        <v>356.225859109472</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15031,28 +15161,28 @@
         <v>0.0929</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5386851307014257</v>
+        <v>0.5217047579169323</v>
       </c>
       <c r="J11" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K11" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03886009373299748</v>
+        <v>0.03704635205368223</v>
       </c>
       <c r="M11" t="n">
-        <v>17.03705391024805</v>
+        <v>16.95040584075934</v>
       </c>
       <c r="N11" t="n">
-        <v>483.8661784082541</v>
+        <v>480.0846256879992</v>
       </c>
       <c r="O11" t="n">
-        <v>21.99695838992869</v>
+        <v>21.91083352335094</v>
       </c>
       <c r="P11" t="n">
-        <v>357.4916465796691</v>
+        <v>357.648637002721</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15109,28 +15239,28 @@
         <v>0.0535</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4302003898348787</v>
+        <v>0.4495477454851882</v>
       </c>
       <c r="J12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03077092180304497</v>
+        <v>0.03392749954869123</v>
       </c>
       <c r="M12" t="n">
-        <v>15.89881407331668</v>
+        <v>15.88986245626613</v>
       </c>
       <c r="N12" t="n">
-        <v>393.0067891802565</v>
+        <v>390.497074544169</v>
       </c>
       <c r="O12" t="n">
-        <v>19.82439883528014</v>
+        <v>19.76099882455765</v>
       </c>
       <c r="P12" t="n">
-        <v>357.2388811420507</v>
+        <v>357.0600070038309</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15187,28 +15317,28 @@
         <v>0.0434</v>
       </c>
       <c r="I13" t="n">
-        <v>0.248564989950928</v>
+        <v>0.2342601895134679</v>
       </c>
       <c r="J13" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01150920832144464</v>
+        <v>0.01038918501195218</v>
       </c>
       <c r="M13" t="n">
-        <v>14.72834644902668</v>
+        <v>14.6503619760861</v>
       </c>
       <c r="N13" t="n">
-        <v>365.7342185609179</v>
+        <v>362.9282684686747</v>
       </c>
       <c r="O13" t="n">
-        <v>19.12417889899898</v>
+        <v>19.05067632575481</v>
       </c>
       <c r="P13" t="n">
-        <v>355.741796190594</v>
+        <v>355.8694501511037</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15265,28 +15395,28 @@
         <v>0.0688</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1752966953254092</v>
+        <v>0.1590533858925567</v>
       </c>
       <c r="J14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007570797359553572</v>
+        <v>0.006325860540527528</v>
       </c>
       <c r="M14" t="n">
-        <v>12.44145431106094</v>
+        <v>12.39243556295631</v>
       </c>
       <c r="N14" t="n">
-        <v>275.7736318006947</v>
+        <v>274.1086240346553</v>
       </c>
       <c r="O14" t="n">
-        <v>16.60643344612848</v>
+        <v>16.55622614108225</v>
       </c>
       <c r="P14" t="n">
-        <v>351.6838823236106</v>
+        <v>351.829179040285</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15343,28 +15473,28 @@
         <v>0.0736</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1312054966523646</v>
+        <v>0.1141803884144215</v>
       </c>
       <c r="J15" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K15" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00582311089749854</v>
+        <v>0.004468313830308213</v>
       </c>
       <c r="M15" t="n">
-        <v>10.8115027679549</v>
+        <v>10.77735331409202</v>
       </c>
       <c r="N15" t="n">
-        <v>199.6986704268191</v>
+        <v>198.8863211851487</v>
       </c>
       <c r="O15" t="n">
-        <v>14.13147799866734</v>
+        <v>14.10270616531269</v>
       </c>
       <c r="P15" t="n">
-        <v>350.0621520396004</v>
+        <v>350.2149125512207</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15421,28 +15551,28 @@
         <v>0.0673</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1415140889959297</v>
+        <v>0.1152467718630633</v>
       </c>
       <c r="J16" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K16" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L16" t="n">
-        <v>0.007301232235405131</v>
+        <v>0.004866047030523513</v>
       </c>
       <c r="M16" t="n">
-        <v>10.45785764920349</v>
+        <v>10.50434053543472</v>
       </c>
       <c r="N16" t="n">
-        <v>184.1791206023937</v>
+        <v>185.1198672118337</v>
       </c>
       <c r="O16" t="n">
-        <v>13.57126083318693</v>
+        <v>13.60587620154739</v>
       </c>
       <c r="P16" t="n">
-        <v>345.0172955471247</v>
+        <v>345.254396996139</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -15499,28 +15629,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07055343803924144</v>
+        <v>0.04274660918630615</v>
       </c>
       <c r="J17" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K17" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001676560390106885</v>
+        <v>0.0006175302045428044</v>
       </c>
       <c r="M17" t="n">
-        <v>10.95987866677034</v>
+        <v>11.00817351983945</v>
       </c>
       <c r="N17" t="n">
-        <v>192.9468795920166</v>
+        <v>194.0397427910653</v>
       </c>
       <c r="O17" t="n">
-        <v>13.89053201256225</v>
+        <v>13.9298148871787</v>
       </c>
       <c r="P17" t="n">
-        <v>343.0963890618275</v>
+        <v>343.3537829371292</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -15577,28 +15707,28 @@
         <v>0.0665</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.01546266466345611</v>
+        <v>-0.03365444717131705</v>
       </c>
       <c r="J18" t="n">
+        <v>109</v>
+      </c>
+      <c r="K18" t="n">
         <v>108</v>
       </c>
-      <c r="K18" t="n">
-        <v>107</v>
-      </c>
       <c r="L18" t="n">
-        <v>7.302403123754519e-05</v>
+        <v>0.0003496292867004591</v>
       </c>
       <c r="M18" t="n">
-        <v>11.75708466728047</v>
+        <v>11.76437246144221</v>
       </c>
       <c r="N18" t="n">
-        <v>219.0527144662231</v>
+        <v>218.3311629045453</v>
       </c>
       <c r="O18" t="n">
-        <v>14.80042953654464</v>
+        <v>14.77603339548694</v>
       </c>
       <c r="P18" t="n">
-        <v>337.3175134344102</v>
+        <v>337.4824113387878</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -15655,28 +15785,28 @@
         <v>0.0692</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07462739027957657</v>
+        <v>0.05101220776278008</v>
       </c>
       <c r="J19" t="n">
+        <v>109</v>
+      </c>
+      <c r="K19" t="n">
         <v>108</v>
       </c>
-      <c r="K19" t="n">
-        <v>107</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.001636016127165241</v>
+        <v>0.0007708362583566108</v>
       </c>
       <c r="M19" t="n">
-        <v>11.61998773592051</v>
+        <v>11.65006502832863</v>
       </c>
       <c r="N19" t="n">
-        <v>220.3083551769988</v>
+        <v>220.3803401805196</v>
       </c>
       <c r="O19" t="n">
-        <v>14.84278798531458</v>
+        <v>14.8452127024344</v>
       </c>
       <c r="P19" t="n">
-        <v>332.5402151085011</v>
+        <v>332.7600100365519</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -15733,28 +15863,28 @@
         <v>0.0704</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1179064126387384</v>
+        <v>0.1051553650796448</v>
       </c>
       <c r="J20" t="n">
+        <v>109</v>
+      </c>
+      <c r="K20" t="n">
         <v>108</v>
       </c>
-      <c r="K20" t="n">
-        <v>107</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.00357582445451643</v>
+        <v>0.002888144062763609</v>
       </c>
       <c r="M20" t="n">
-        <v>13.13058551797084</v>
+        <v>13.08468535739474</v>
       </c>
       <c r="N20" t="n">
-        <v>251.1169637270173</v>
+        <v>249.4075188793554</v>
       </c>
       <c r="O20" t="n">
-        <v>15.84667043031492</v>
+        <v>15.79264128888374</v>
       </c>
       <c r="P20" t="n">
-        <v>325.5867999339229</v>
+        <v>325.705478482303</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -15811,28 +15941,28 @@
         <v>0.0697</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2960297447764611</v>
+        <v>0.2886382128255059</v>
       </c>
       <c r="J21" t="n">
+        <v>109</v>
+      </c>
+      <c r="K21" t="n">
         <v>108</v>
       </c>
-      <c r="K21" t="n">
-        <v>107</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02221153947158017</v>
+        <v>0.02147865000529703</v>
       </c>
       <c r="M21" t="n">
-        <v>13.039140973506</v>
+        <v>12.9604040405385</v>
       </c>
       <c r="N21" t="n">
-        <v>250.0748877938615</v>
+        <v>247.9662769395571</v>
       </c>
       <c r="O21" t="n">
-        <v>15.81375628349765</v>
+        <v>15.74694500338263</v>
       </c>
       <c r="P21" t="n">
-        <v>316.9526454445217</v>
+        <v>317.021441069209</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -15889,28 +16019,28 @@
         <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.302112216577237</v>
+        <v>0.295886356488375</v>
       </c>
       <c r="J22" t="n">
+        <v>109</v>
+      </c>
+      <c r="K22" t="n">
         <v>108</v>
       </c>
-      <c r="K22" t="n">
-        <v>107</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.0259267822588507</v>
+        <v>0.02529772239261263</v>
       </c>
       <c r="M22" t="n">
-        <v>12.2269952219669</v>
+        <v>12.15243693150665</v>
       </c>
       <c r="N22" t="n">
-        <v>222.2862967590817</v>
+        <v>220.3748763489295</v>
       </c>
       <c r="O22" t="n">
-        <v>14.90926882040436</v>
+        <v>14.84502867457417</v>
       </c>
       <c r="P22" t="n">
-        <v>311.160430558264</v>
+        <v>311.2183768590945</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -15967,28 +16097,28 @@
         <v>0.0565</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1336075220052362</v>
+        <v>0.1257847791242333</v>
       </c>
       <c r="J23" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K23" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005487282853343212</v>
+        <v>0.004945344891361336</v>
       </c>
       <c r="M23" t="n">
-        <v>11.49054688659595</v>
+        <v>11.42598484695821</v>
       </c>
       <c r="N23" t="n">
-        <v>213.338123424887</v>
+        <v>211.5781499229699</v>
       </c>
       <c r="O23" t="n">
-        <v>14.60609884345875</v>
+        <v>14.54572617379311</v>
       </c>
       <c r="P23" t="n">
-        <v>307.8642005468122</v>
+        <v>307.9358998169636</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -16045,28 +16175,28 @@
         <v>0.061</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1821971214095766</v>
+        <v>0.1696714009462698</v>
       </c>
       <c r="J24" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K24" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L24" t="n">
-        <v>0.007612786589306197</v>
+        <v>0.006710384946218895</v>
       </c>
       <c r="M24" t="n">
-        <v>13.40450968921322</v>
+        <v>13.34339120449872</v>
       </c>
       <c r="N24" t="n">
-        <v>272.7477483038741</v>
+        <v>270.7159895472522</v>
       </c>
       <c r="O24" t="n">
-        <v>16.5150763941277</v>
+        <v>16.45344916870782</v>
       </c>
       <c r="P24" t="n">
-        <v>301.8950812189003</v>
+        <v>302.0148407226908</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -16123,28 +16253,28 @@
         <v>0.0519</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1383209991858137</v>
+        <v>0.1310531642410636</v>
       </c>
       <c r="J25" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K25" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004535320152229683</v>
+        <v>0.004141546443547806</v>
       </c>
       <c r="M25" t="n">
-        <v>13.25851507017232</v>
+        <v>13.17640492362898</v>
       </c>
       <c r="N25" t="n">
-        <v>267.9407634903055</v>
+        <v>265.6059759755435</v>
       </c>
       <c r="O25" t="n">
-        <v>16.36889622089118</v>
+        <v>16.29742237212816</v>
       </c>
       <c r="P25" t="n">
-        <v>297.1354191017825</v>
+        <v>297.2040030827849</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -16201,28 +16331,28 @@
         <v>0.0309</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5416614307632335</v>
+        <v>0.5272694229810034</v>
       </c>
       <c r="J26" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K26" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0400352574528231</v>
+        <v>0.03860066863026568</v>
       </c>
       <c r="M26" t="n">
-        <v>17.45033366440788</v>
+        <v>17.3658467629629</v>
       </c>
       <c r="N26" t="n">
-        <v>447.2103845261531</v>
+        <v>443.6592578274768</v>
       </c>
       <c r="O26" t="n">
-        <v>21.14734934988669</v>
+        <v>21.06322049990164</v>
       </c>
       <c r="P26" t="n">
-        <v>282.6424491443535</v>
+        <v>282.7791600222968</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -16279,28 +16409,28 @@
         <v>0.0427</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2849943940234518</v>
+        <v>0.2669777110302587</v>
       </c>
       <c r="J27" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K27" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01358955489479041</v>
+        <v>0.01211347570229648</v>
       </c>
       <c r="M27" t="n">
-        <v>15.39797651419291</v>
+        <v>15.37886911488673</v>
       </c>
       <c r="N27" t="n">
-        <v>382.7447607472017</v>
+        <v>380.2793021862246</v>
       </c>
       <c r="O27" t="n">
-        <v>19.5638636456913</v>
+        <v>19.50075132363429</v>
       </c>
       <c r="P27" t="n">
-        <v>283.5495550851913</v>
+        <v>283.7181183183467</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -16357,28 +16487,28 @@
         <v>0.0517</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1739407841952238</v>
+        <v>-0.1879005891034197</v>
       </c>
       <c r="J28" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K28" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L28" t="n">
-        <v>0.007474562206252089</v>
+        <v>0.008840006896921437</v>
       </c>
       <c r="M28" t="n">
-        <v>12.69550791363122</v>
+        <v>12.67208403806194</v>
       </c>
       <c r="N28" t="n">
-        <v>250.9908232670744</v>
+        <v>249.2936943741076</v>
       </c>
       <c r="O28" t="n">
-        <v>15.84268989998461</v>
+        <v>15.78903715791775</v>
       </c>
       <c r="P28" t="n">
-        <v>290.4998158362446</v>
+        <v>290.6341405370108</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -16435,28 +16565,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.09189459604494715</v>
+        <v>-0.1008478506451785</v>
       </c>
       <c r="J29" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K29" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002284882486894957</v>
+        <v>0.00279391331862977</v>
       </c>
       <c r="M29" t="n">
-        <v>12.81717733661109</v>
+        <v>12.75540816484099</v>
       </c>
       <c r="N29" t="n">
-        <v>244.6398530113821</v>
+        <v>242.7082910746435</v>
       </c>
       <c r="O29" t="n">
-        <v>15.64096713798038</v>
+        <v>15.57909789027091</v>
       </c>
       <c r="P29" t="n">
-        <v>286.7587471200209</v>
+        <v>286.8402623636308</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -16513,28 +16643,28 @@
         <v>0.0708</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1337560830535847</v>
+        <v>0.1233572155808836</v>
       </c>
       <c r="J30" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K30" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L30" t="n">
-        <v>0.005699746097559411</v>
+        <v>0.004924713619707366</v>
       </c>
       <c r="M30" t="n">
-        <v>11.32566747767286</v>
+        <v>11.28900594488991</v>
       </c>
       <c r="N30" t="n">
-        <v>207.058804536917</v>
+        <v>205.5812024726394</v>
       </c>
       <c r="O30" t="n">
-        <v>14.38953802374895</v>
+        <v>14.33810316857287</v>
       </c>
       <c r="P30" t="n">
-        <v>282.787948260899</v>
+        <v>282.8826251413357</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -16591,28 +16721,28 @@
         <v>0.0684</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1054842576710843</v>
+        <v>0.09624782657049549</v>
       </c>
       <c r="J31" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K31" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L31" t="n">
-        <v>0.003215685961279524</v>
+        <v>0.002720421089964731</v>
       </c>
       <c r="M31" t="n">
-        <v>11.57875878477596</v>
+        <v>11.52798997172911</v>
       </c>
       <c r="N31" t="n">
-        <v>228.8270936237308</v>
+        <v>227.0607050628112</v>
       </c>
       <c r="O31" t="n">
-        <v>15.1270318841381</v>
+        <v>15.0685336069178</v>
       </c>
       <c r="P31" t="n">
-        <v>281.6128877417672</v>
+        <v>281.6969811764866</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -16669,28 +16799,28 @@
         <v>0.0701</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.04722220224303401</v>
+        <v>-0.06509662458942525</v>
       </c>
       <c r="J32" t="n">
+        <v>109</v>
+      </c>
+      <c r="K32" t="n">
         <v>108</v>
       </c>
-      <c r="K32" t="n">
-        <v>107</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.0005470456747832531</v>
+        <v>0.001052031653488772</v>
       </c>
       <c r="M32" t="n">
-        <v>12.81163699106971</v>
+        <v>12.78785567076588</v>
       </c>
       <c r="N32" t="n">
-        <v>265.2695076690217</v>
+        <v>264.031743446551</v>
       </c>
       <c r="O32" t="n">
-        <v>16.28709635475341</v>
+        <v>16.24905361695108</v>
       </c>
       <c r="P32" t="n">
-        <v>286.2625381886655</v>
+        <v>286.4283531332816</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -16747,28 +16877,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3961896192242702</v>
+        <v>-0.4140640981430875</v>
       </c>
       <c r="J33" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K33" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04036335591632745</v>
+        <v>0.04443834999624841</v>
       </c>
       <c r="M33" t="n">
-        <v>12.17055229687462</v>
+        <v>12.14341247240303</v>
       </c>
       <c r="N33" t="n">
-        <v>237.0721856131497</v>
+        <v>236.0362701564014</v>
       </c>
       <c r="O33" t="n">
-        <v>15.39714861957076</v>
+        <v>15.36347194342481</v>
       </c>
       <c r="P33" t="n">
-        <v>303.439980035896</v>
+        <v>303.6095700458138</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -16825,28 +16955,28 @@
         <v>0.0675</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1335133470037266</v>
+        <v>-0.1565077155246846</v>
       </c>
       <c r="J34" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K34" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L34" t="n">
-        <v>0.00501217871583659</v>
+        <v>0.006931865350582211</v>
       </c>
       <c r="M34" t="n">
-        <v>12.28861104400119</v>
+        <v>12.28875539182051</v>
       </c>
       <c r="N34" t="n">
-        <v>231.5152123372834</v>
+        <v>231.3684026083594</v>
       </c>
       <c r="O34" t="n">
-        <v>15.21562395491172</v>
+        <v>15.21079888133294</v>
       </c>
       <c r="P34" t="n">
-        <v>310.8059822833261</v>
+        <v>311.0186359683133</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -16903,28 +17033,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.08798932012349152</v>
+        <v>-0.1032955593354671</v>
       </c>
       <c r="J35" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K35" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L35" t="n">
-        <v>0.001939804854265592</v>
+        <v>0.0027078818533397</v>
       </c>
       <c r="M35" t="n">
-        <v>13.47197907822746</v>
+        <v>13.42416841811261</v>
       </c>
       <c r="N35" t="n">
-        <v>259.7213997262209</v>
+        <v>258.1422035335192</v>
       </c>
       <c r="O35" t="n">
-        <v>16.11587415333778</v>
+        <v>16.06680439706413</v>
       </c>
       <c r="P35" t="n">
-        <v>318.3373456177258</v>
+        <v>318.4802256457657</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -16981,28 +17111,28 @@
         <v>0.0713</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1298436525854989</v>
+        <v>-0.1388767360419329</v>
       </c>
       <c r="J36" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K36" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L36" t="n">
-        <v>0.005126353280069496</v>
+        <v>0.005952839840068669</v>
       </c>
       <c r="M36" t="n">
-        <v>12.91161086589002</v>
+        <v>12.83353584039688</v>
       </c>
       <c r="N36" t="n">
-        <v>216.0773753472042</v>
+        <v>214.2915539747086</v>
       </c>
       <c r="O36" t="n">
-        <v>14.69957058376891</v>
+        <v>14.63870055622112</v>
       </c>
       <c r="P36" t="n">
-        <v>334.9754417481196</v>
+        <v>335.0589633594651</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -17059,28 +17189,28 @@
         <v>0.0823</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.01129930314052824</v>
+        <v>-0.01345603156767761</v>
       </c>
       <c r="J37" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K37" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L37" t="n">
-        <v>4.324034005875887e-05</v>
+        <v>6.2382578163378e-05</v>
       </c>
       <c r="M37" t="n">
-        <v>11.99210812374794</v>
+        <v>11.88835762434604</v>
       </c>
       <c r="N37" t="n">
-        <v>194.9862079075925</v>
+        <v>193.1109247125734</v>
       </c>
       <c r="O37" t="n">
-        <v>13.96374619891068</v>
+        <v>13.89643568374903</v>
       </c>
       <c r="P37" t="n">
-        <v>329.2499232872484</v>
+        <v>329.2698648093587</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -17118,7 +17248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL109"/>
+  <dimension ref="A1:AL110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36957,6 +37087,198 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>-34.48236461818888,173.00279540302645</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>-34.48302952761015,173.0023995418302</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>-34.48372836180873,173.0020830298592</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-34.484372903132844,173.00163955990683</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-34.48515290338523,173.0014697614778</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-34.485909740902194,173.0013313779296</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-34.48666189669594,173.00130272426966</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-34.48740264336078,173.00129654307457</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>-34.48814483139888,173.00125492842733</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>-34.48888484942607,173.00132720346213</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>-34.4895929336666,173.00167409966312</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>-34.49036188806631,173.00150622051208</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>-34.491103840123785,173.00155966302736</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>-34.491840594297656,173.00165566744656</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>-34.492587357102494,173.00166956115788</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>-34.49332585968976,173.0017511242066</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>-34.49406122782951,173.00185833278198</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>-34.494804080931374,173.00192869905035</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>-34.49553767171121,173.00208668500625</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>-34.49626984438401,173.00223324464164</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>-34.49700700771634,173.0023323186617</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>-34.497750025090355,173.00238994658008</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>-34.49849248397327,173.0024617220669</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>-34.49923660646077,173.002591129807</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>-34.499986029141965,173.00268826690322</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>-34.500725958916526,173.0027834000985</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>-34.50145499157002,173.002941773846</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>-34.5021776449862,173.0031371542204</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>-34.50290056756777,173.0033309350573</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>-34.50361991429926,173.00350002603156</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>-34.50429924454382,173.00360255228216</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>-34.50498451497242,173.00374755375336</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>-34.50571655380695,173.00392505488924</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>-34.50644672774201,173.00413570793893</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>-34.50722481076318,173.00441891173014</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>-34.507958042470726,173.00477524434376</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0007/nzd0007.xlsx
+++ b/data/nzd0007/nzd0007.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL110"/>
+  <dimension ref="A1:AL111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13157,6 +13157,126 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>305.87</v>
+      </c>
+      <c r="C111" t="n">
+        <v>307.61</v>
+      </c>
+      <c r="D111" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="E111" t="n">
+        <v>314.37</v>
+      </c>
+      <c r="F111" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="G111" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="H111" t="n">
+        <v>355.93</v>
+      </c>
+      <c r="I111" t="n">
+        <v>358.36</v>
+      </c>
+      <c r="J111" t="n">
+        <v>357.54</v>
+      </c>
+      <c r="K111" t="n">
+        <v>360.81</v>
+      </c>
+      <c r="L111" t="n">
+        <v>380.8</v>
+      </c>
+      <c r="M111" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="N111" t="n">
+        <v>347.44</v>
+      </c>
+      <c r="O111" t="n">
+        <v>343.86</v>
+      </c>
+      <c r="P111" t="n">
+        <v>331.73</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>327.73</v>
+      </c>
+      <c r="R111" t="n">
+        <v>325.16</v>
+      </c>
+      <c r="S111" t="n">
+        <v>319.55</v>
+      </c>
+      <c r="T111" t="n">
+        <v>321.81</v>
+      </c>
+      <c r="U111" t="n">
+        <v>319.74</v>
+      </c>
+      <c r="V111" t="n">
+        <v>313.72</v>
+      </c>
+      <c r="W111" t="n">
+        <v>305.91</v>
+      </c>
+      <c r="X111" t="n">
+        <v>297.51</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>294.75</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>285.21</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>277.67</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>274.19</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>277.19</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>278.98</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>274.56</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>281.45</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>292.31</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>305.64</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>325.66</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>327.14</v>
+      </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13168,7 +13288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14291,6 +14411,16 @@
       </c>
       <c r="B112" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -14459,28 +14589,28 @@
         <v>0.0633</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06093721531361151</v>
+        <v>-0.06417756858707477</v>
       </c>
       <c r="J2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001084502867483961</v>
+        <v>0.001223006007027738</v>
       </c>
       <c r="M2" t="n">
-        <v>12.92662851038778</v>
+        <v>12.8005486257261</v>
       </c>
       <c r="N2" t="n">
-        <v>238.8308034203139</v>
+        <v>236.2204115689058</v>
       </c>
       <c r="O2" t="n">
-        <v>15.45415165644216</v>
+        <v>15.36946360706534</v>
       </c>
       <c r="P2" t="n">
-        <v>309.4695736320803</v>
+        <v>309.499416115075</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14537,28 +14667,28 @@
         <v>0.047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07966950473470637</v>
+        <v>0.08720585521628048</v>
       </c>
       <c r="J3" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001556520399431882</v>
+        <v>0.001893042053264682</v>
       </c>
       <c r="M3" t="n">
-        <v>13.11846441650753</v>
+        <v>13.02351504609312</v>
       </c>
       <c r="N3" t="n">
-        <v>277.5935667022254</v>
+        <v>274.7818628531152</v>
       </c>
       <c r="O3" t="n">
-        <v>16.66113941788572</v>
+        <v>16.57654556453531</v>
       </c>
       <c r="P3" t="n">
-        <v>300.7890128021286</v>
+        <v>300.7176509710189</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14615,28 +14745,28 @@
         <v>0.0373</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2262507369425404</v>
+        <v>0.2505743904568127</v>
       </c>
       <c r="J4" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01042233854470009</v>
+        <v>0.01285916633327189</v>
       </c>
       <c r="M4" t="n">
-        <v>14.51850284873469</v>
+        <v>14.53963059215096</v>
       </c>
       <c r="N4" t="n">
-        <v>322.9467020206804</v>
+        <v>321.8089511461866</v>
       </c>
       <c r="O4" t="n">
-        <v>17.97071790498867</v>
+        <v>17.93903428688921</v>
       </c>
       <c r="P4" t="n">
-        <v>296.5444335142799</v>
+        <v>296.3080201692172</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14693,28 +14823,28 @@
         <v>0.0321</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2157597804379667</v>
+        <v>-0.2025066448973497</v>
       </c>
       <c r="J5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01123210408229536</v>
+        <v>0.01004656232438694</v>
       </c>
       <c r="M5" t="n">
-        <v>13.72198744981922</v>
+        <v>13.64988745076612</v>
       </c>
       <c r="N5" t="n">
-        <v>293.2285948039512</v>
+        <v>290.7948025246171</v>
       </c>
       <c r="O5" t="n">
-        <v>17.12391879226105</v>
+        <v>17.05270660407365</v>
       </c>
       <c r="P5" t="n">
-        <v>311.6042260058646</v>
+        <v>311.4851125340024</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14771,28 +14901,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05015594929900398</v>
+        <v>0.06500983572502822</v>
       </c>
       <c r="J6" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004877474267394044</v>
+        <v>0.0008307961321309953</v>
       </c>
       <c r="M6" t="n">
-        <v>14.22246131922984</v>
+        <v>14.16524326521627</v>
       </c>
       <c r="N6" t="n">
-        <v>335.6278896119471</v>
+        <v>332.9151654122036</v>
       </c>
       <c r="O6" t="n">
-        <v>18.32014982504093</v>
+        <v>18.24596298944519</v>
       </c>
       <c r="P6" t="n">
-        <v>329.9572356189169</v>
+        <v>329.8125676470063</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14849,28 +14979,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0939109599202916</v>
+        <v>-0.07897480385422478</v>
       </c>
       <c r="J7" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001341165290280166</v>
+        <v>0.0009625258910629375</v>
       </c>
       <c r="M7" t="n">
-        <v>15.96767107380657</v>
+        <v>15.86803485849711</v>
       </c>
       <c r="N7" t="n">
-        <v>393.0891669889938</v>
+        <v>389.5328753643378</v>
       </c>
       <c r="O7" t="n">
-        <v>19.8264764138511</v>
+        <v>19.73658722688241</v>
       </c>
       <c r="P7" t="n">
-        <v>349.2063403064984</v>
+        <v>349.0491511459758</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14927,28 +15057,28 @@
         <v>0.1955</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1298188384521401</v>
+        <v>0.1405355742235672</v>
       </c>
       <c r="J8" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003083354004021821</v>
+        <v>0.003668670336343327</v>
       </c>
       <c r="M8" t="n">
-        <v>14.17736321826898</v>
+        <v>14.06052377147866</v>
       </c>
       <c r="N8" t="n">
-        <v>325.2072394649171</v>
+        <v>321.9135747320866</v>
       </c>
       <c r="O8" t="n">
-        <v>18.03350324992116</v>
+        <v>17.941950137376</v>
       </c>
       <c r="P8" t="n">
-        <v>346.4831010678326</v>
+        <v>346.3702983257932</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15005,28 +15135,28 @@
         <v>0.1138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02556703729407084</v>
+        <v>0.03300023012988491</v>
       </c>
       <c r="J9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001067412194142303</v>
+        <v>0.0001808298018705079</v>
       </c>
       <c r="M9" t="n">
-        <v>14.58813241426916</v>
+        <v>14.45488248997447</v>
       </c>
       <c r="N9" t="n">
-        <v>385.4939362773504</v>
+        <v>381.4580126980066</v>
       </c>
       <c r="O9" t="n">
-        <v>19.63399949774244</v>
+        <v>19.53095012276685</v>
       </c>
       <c r="P9" t="n">
-        <v>353.3573873986759</v>
+        <v>353.2830013331564</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15083,28 +15213,28 @@
         <v>0.0704</v>
       </c>
       <c r="I10" t="n">
-        <v>0.337792815967658</v>
+        <v>0.3250473536507549</v>
       </c>
       <c r="J10" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01908039632690461</v>
+        <v>0.01797608425927266</v>
       </c>
       <c r="M10" t="n">
-        <v>15.9795025103822</v>
+        <v>15.9072224422954</v>
       </c>
       <c r="N10" t="n">
-        <v>397.608218767784</v>
+        <v>393.8091772119072</v>
       </c>
       <c r="O10" t="n">
-        <v>19.94011581630819</v>
+        <v>19.84462590254367</v>
       </c>
       <c r="P10" t="n">
-        <v>356.225859109472</v>
+        <v>356.345258755496</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15161,28 +15291,28 @@
         <v>0.0929</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5217047579169323</v>
+        <v>0.5053555069569945</v>
       </c>
       <c r="J11" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K11" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03704635205368223</v>
+        <v>0.0353214977459565</v>
       </c>
       <c r="M11" t="n">
-        <v>16.95040584075934</v>
+        <v>16.86136883824032</v>
       </c>
       <c r="N11" t="n">
-        <v>480.0846256879992</v>
+        <v>476.331467221567</v>
       </c>
       <c r="O11" t="n">
-        <v>21.91083352335094</v>
+        <v>21.82501929487273</v>
       </c>
       <c r="P11" t="n">
-        <v>357.648637002721</v>
+        <v>357.8008898550318</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15239,28 +15369,28 @@
         <v>0.0535</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4495477454851882</v>
+        <v>0.46799894887752</v>
       </c>
       <c r="J12" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03392749954869123</v>
+        <v>0.03712422166357399</v>
       </c>
       <c r="M12" t="n">
-        <v>15.88986245626613</v>
+        <v>15.87521958718525</v>
       </c>
       <c r="N12" t="n">
-        <v>390.497074544169</v>
+        <v>387.9488223015954</v>
       </c>
       <c r="O12" t="n">
-        <v>19.76099882455765</v>
+        <v>19.69641648375652</v>
       </c>
       <c r="P12" t="n">
-        <v>357.0600070038309</v>
+        <v>356.8881796612859</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15317,28 +15447,28 @@
         <v>0.0434</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2342601895134679</v>
+        <v>0.2179970397007688</v>
       </c>
       <c r="J13" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01038918501195218</v>
+        <v>0.009135045842952438</v>
       </c>
       <c r="M13" t="n">
-        <v>14.6503619760861</v>
+        <v>14.58219475656934</v>
       </c>
       <c r="N13" t="n">
-        <v>362.9282684686747</v>
+        <v>360.4496500520449</v>
       </c>
       <c r="O13" t="n">
-        <v>19.05067632575481</v>
+        <v>18.98551158257383</v>
       </c>
       <c r="P13" t="n">
-        <v>355.8694501511037</v>
+        <v>356.0156095462981</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15395,28 +15525,28 @@
         <v>0.0688</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1590533858925567</v>
+        <v>0.1459303983734409</v>
       </c>
       <c r="J14" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L14" t="n">
-        <v>0.006325860540527528</v>
+        <v>0.005407960631493625</v>
       </c>
       <c r="M14" t="n">
-        <v>12.39243556295631</v>
+        <v>12.32982267698232</v>
       </c>
       <c r="N14" t="n">
-        <v>274.1086240346553</v>
+        <v>272.1420578711435</v>
       </c>
       <c r="O14" t="n">
-        <v>16.55622614108225</v>
+        <v>16.49672870211375</v>
       </c>
       <c r="P14" t="n">
-        <v>351.829179040285</v>
+        <v>351.9473825319869</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15473,28 +15603,28 @@
         <v>0.0736</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1141803884144215</v>
+        <v>0.09983617371998973</v>
       </c>
       <c r="J15" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K15" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004468313830308213</v>
+        <v>0.003464406189187641</v>
       </c>
       <c r="M15" t="n">
-        <v>10.77735331409202</v>
+        <v>10.73293848991636</v>
       </c>
       <c r="N15" t="n">
-        <v>198.8863211851487</v>
+        <v>197.7934862175143</v>
       </c>
       <c r="O15" t="n">
-        <v>14.10270616531269</v>
+        <v>14.06390721732457</v>
       </c>
       <c r="P15" t="n">
-        <v>350.2149125512207</v>
+        <v>350.3444990769104</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15551,28 +15681,28 @@
         <v>0.0673</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1152467718630633</v>
+        <v>0.09012236365655457</v>
       </c>
       <c r="J16" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K16" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004866047030523513</v>
+        <v>0.002990683697169261</v>
       </c>
       <c r="M16" t="n">
-        <v>10.50434053543472</v>
+        <v>10.54905856870271</v>
       </c>
       <c r="N16" t="n">
-        <v>185.1198672118337</v>
+        <v>185.8975445971609</v>
       </c>
       <c r="O16" t="n">
-        <v>13.60587620154739</v>
+        <v>13.63442498227046</v>
       </c>
       <c r="P16" t="n">
-        <v>345.254396996139</v>
+        <v>345.4827336306223</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -15629,28 +15759,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04274660918630615</v>
+        <v>0.01706276794688672</v>
       </c>
       <c r="J17" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K17" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0006175302045428044</v>
+        <v>9.883761493278964e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>11.00817351983945</v>
+        <v>11.04284503233575</v>
       </c>
       <c r="N17" t="n">
-        <v>194.0397427910653</v>
+        <v>194.7736873997084</v>
       </c>
       <c r="O17" t="n">
-        <v>13.9298148871787</v>
+        <v>13.95613440031689</v>
       </c>
       <c r="P17" t="n">
-        <v>343.3537829371292</v>
+        <v>343.5930513264728</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -15707,28 +15837,28 @@
         <v>0.0665</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.03365444717131705</v>
+        <v>-0.05066628529125192</v>
       </c>
       <c r="J18" t="n">
+        <v>110</v>
+      </c>
+      <c r="K18" t="n">
         <v>109</v>
       </c>
-      <c r="K18" t="n">
-        <v>108</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.0003496292867004591</v>
+        <v>0.0008010567358921472</v>
       </c>
       <c r="M18" t="n">
-        <v>11.76437246144221</v>
+        <v>11.76622891794796</v>
       </c>
       <c r="N18" t="n">
-        <v>218.3311629045453</v>
+        <v>217.49752849892</v>
       </c>
       <c r="O18" t="n">
-        <v>14.77603339548694</v>
+        <v>14.74779741178051</v>
       </c>
       <c r="P18" t="n">
-        <v>337.4824113387878</v>
+        <v>337.6376406381205</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -15785,28 +15915,28 @@
         <v>0.0692</v>
       </c>
       <c r="I19" t="n">
-        <v>0.05101220776278008</v>
+        <v>0.02891386267717608</v>
       </c>
       <c r="J19" t="n">
+        <v>110</v>
+      </c>
+      <c r="K19" t="n">
         <v>109</v>
       </c>
-      <c r="K19" t="n">
-        <v>108</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.0007708362583566108</v>
+        <v>0.0002498150621053075</v>
       </c>
       <c r="M19" t="n">
-        <v>11.65006502832863</v>
+        <v>11.67797522225657</v>
       </c>
       <c r="N19" t="n">
-        <v>220.3803401805196</v>
+        <v>220.2512630917714</v>
       </c>
       <c r="O19" t="n">
-        <v>14.8452127024344</v>
+        <v>14.84086463423784</v>
       </c>
       <c r="P19" t="n">
-        <v>332.7600100365519</v>
+        <v>332.967007577334</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -15863,28 +15993,28 @@
         <v>0.0704</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1051553650796448</v>
+        <v>0.09503910869126168</v>
       </c>
       <c r="J20" t="n">
+        <v>110</v>
+      </c>
+      <c r="K20" t="n">
         <v>109</v>
       </c>
-      <c r="K20" t="n">
-        <v>108</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.002888144062763609</v>
+        <v>0.002396583722348411</v>
       </c>
       <c r="M20" t="n">
-        <v>13.08468535739474</v>
+        <v>13.02391143174509</v>
       </c>
       <c r="N20" t="n">
-        <v>249.4075188793554</v>
+        <v>247.5160342209701</v>
       </c>
       <c r="O20" t="n">
-        <v>15.79264128888374</v>
+        <v>15.73264231529371</v>
       </c>
       <c r="P20" t="n">
-        <v>325.705478482303</v>
+        <v>325.8002385281889</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -15941,28 +16071,28 @@
         <v>0.0697</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2886382128255059</v>
+        <v>0.2812303153936411</v>
       </c>
       <c r="J21" t="n">
+        <v>110</v>
+      </c>
+      <c r="K21" t="n">
         <v>109</v>
       </c>
-      <c r="K21" t="n">
-        <v>108</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02147865000529703</v>
+        <v>0.02073444242613376</v>
       </c>
       <c r="M21" t="n">
-        <v>12.9604040405385</v>
+        <v>12.88278163838243</v>
       </c>
       <c r="N21" t="n">
-        <v>247.9662769395571</v>
+        <v>245.9040563228538</v>
       </c>
       <c r="O21" t="n">
-        <v>15.74694500338263</v>
+        <v>15.68132827036198</v>
       </c>
       <c r="P21" t="n">
-        <v>317.021441069209</v>
+        <v>317.0908316296705</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -16019,28 +16149,28 @@
         <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.295886356488375</v>
+        <v>0.2878685937372238</v>
       </c>
       <c r="J22" t="n">
+        <v>110</v>
+      </c>
+      <c r="K22" t="n">
         <v>109</v>
       </c>
-      <c r="K22" t="n">
-        <v>108</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.02529772239261263</v>
+        <v>0.02434793956282333</v>
       </c>
       <c r="M22" t="n">
-        <v>12.15243693150665</v>
+        <v>12.09077049588617</v>
       </c>
       <c r="N22" t="n">
-        <v>220.3748763489295</v>
+        <v>218.6022509780495</v>
       </c>
       <c r="O22" t="n">
-        <v>14.84502867457417</v>
+        <v>14.78520378547585</v>
       </c>
       <c r="P22" t="n">
-        <v>311.2183768590945</v>
+        <v>311.2934800926459</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -16097,28 +16227,28 @@
         <v>0.0565</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1257847791242333</v>
+        <v>0.1176917584535438</v>
       </c>
       <c r="J23" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K23" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004945344891361336</v>
+        <v>0.004400577365030856</v>
       </c>
       <c r="M23" t="n">
-        <v>11.42598484695821</v>
+        <v>11.36581838626511</v>
       </c>
       <c r="N23" t="n">
-        <v>211.5781499229699</v>
+        <v>209.8753849645623</v>
       </c>
       <c r="O23" t="n">
-        <v>14.54572617379311</v>
+        <v>14.48707648093853</v>
       </c>
       <c r="P23" t="n">
-        <v>307.9358998169636</v>
+        <v>308.0105605863842</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -16175,28 +16305,28 @@
         <v>0.061</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1696714009462698</v>
+        <v>0.1555348529095272</v>
       </c>
       <c r="J24" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K24" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L24" t="n">
-        <v>0.006710384946218895</v>
+        <v>0.005726443312051299</v>
       </c>
       <c r="M24" t="n">
-        <v>13.34339120449872</v>
+        <v>13.29108363977522</v>
       </c>
       <c r="N24" t="n">
-        <v>270.7159895472522</v>
+        <v>268.9001853555052</v>
       </c>
       <c r="O24" t="n">
-        <v>16.45344916870782</v>
+        <v>16.39817628138889</v>
       </c>
       <c r="P24" t="n">
-        <v>302.0148407226908</v>
+        <v>302.1508527402226</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -16253,28 +16383,28 @@
         <v>0.0519</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1310531642410636</v>
+        <v>0.1218461695905215</v>
       </c>
       <c r="J25" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K25" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004141546443547806</v>
+        <v>0.003639537232209222</v>
       </c>
       <c r="M25" t="n">
-        <v>13.17640492362898</v>
+        <v>13.10776069284124</v>
       </c>
       <c r="N25" t="n">
-        <v>265.6059759755435</v>
+        <v>263.4408400215042</v>
       </c>
       <c r="O25" t="n">
-        <v>16.29742237212816</v>
+        <v>16.23086072953324</v>
       </c>
       <c r="P25" t="n">
-        <v>297.2040030827849</v>
+        <v>297.2914356904808</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -16331,28 +16461,28 @@
         <v>0.0309</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5272694229810034</v>
+        <v>0.5091724401374191</v>
       </c>
       <c r="J26" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K26" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03860066863026568</v>
+        <v>0.03659905810743969</v>
       </c>
       <c r="M26" t="n">
-        <v>17.3658467629629</v>
+        <v>17.30318924802332</v>
       </c>
       <c r="N26" t="n">
-        <v>443.6592578274768</v>
+        <v>440.6471408847539</v>
       </c>
       <c r="O26" t="n">
-        <v>21.06322049990164</v>
+        <v>20.99159691125842</v>
       </c>
       <c r="P26" t="n">
-        <v>282.7791600222968</v>
+        <v>282.9521587237729</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -16409,28 +16539,28 @@
         <v>0.0427</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2669777110302587</v>
+        <v>0.2466512453018694</v>
       </c>
       <c r="J27" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K27" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01211347570229648</v>
+        <v>0.01049016030634931</v>
       </c>
       <c r="M27" t="n">
-        <v>15.37886911488673</v>
+        <v>15.37512423115409</v>
       </c>
       <c r="N27" t="n">
-        <v>380.2793021862246</v>
+        <v>378.2410415187089</v>
       </c>
       <c r="O27" t="n">
-        <v>19.50075132363429</v>
+        <v>19.44842002628257</v>
       </c>
       <c r="P27" t="n">
-        <v>283.7181183183467</v>
+        <v>283.9095370181527</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -16487,28 +16617,28 @@
         <v>0.0517</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1879005891034197</v>
+        <v>-0.2061643653635009</v>
       </c>
       <c r="J28" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K28" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L28" t="n">
-        <v>0.008840006896921437</v>
+        <v>0.01075353859225647</v>
       </c>
       <c r="M28" t="n">
-        <v>12.67208403806194</v>
+        <v>12.67763558867127</v>
       </c>
       <c r="N28" t="n">
-        <v>249.2936943741076</v>
+        <v>248.1572913357633</v>
       </c>
       <c r="O28" t="n">
-        <v>15.78903715791775</v>
+        <v>15.75300896133063</v>
       </c>
       <c r="P28" t="n">
-        <v>290.6341405370108</v>
+        <v>290.8109735459403</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -16565,28 +16695,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1008478506451785</v>
+        <v>-0.1112630403669867</v>
       </c>
       <c r="J29" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K29" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L29" t="n">
-        <v>0.00279391331862977</v>
+        <v>0.003449677831846132</v>
       </c>
       <c r="M29" t="n">
-        <v>12.75540816484099</v>
+        <v>12.70321804338005</v>
       </c>
       <c r="N29" t="n">
-        <v>242.7082910746435</v>
+        <v>240.9351209074662</v>
       </c>
       <c r="O29" t="n">
-        <v>15.57909789027091</v>
+        <v>15.52208494073738</v>
       </c>
       <c r="P29" t="n">
-        <v>286.8402623636308</v>
+        <v>286.9357086925357</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -16643,28 +16773,28 @@
         <v>0.0708</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1233572155808836</v>
+        <v>0.1127094929228719</v>
       </c>
       <c r="J30" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K30" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L30" t="n">
-        <v>0.004924713619707366</v>
+        <v>0.004174459826171373</v>
       </c>
       <c r="M30" t="n">
-        <v>11.28900594488991</v>
+        <v>11.25423187068384</v>
       </c>
       <c r="N30" t="n">
-        <v>205.5812024726394</v>
+        <v>204.1651138661713</v>
       </c>
       <c r="O30" t="n">
-        <v>14.33810316857287</v>
+        <v>14.28863582943352</v>
       </c>
       <c r="P30" t="n">
-        <v>282.8826251413357</v>
+        <v>282.9802024362338</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -16721,28 +16851,28 @@
         <v>0.0684</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09624782657049549</v>
+        <v>0.08503829296390146</v>
       </c>
       <c r="J31" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K31" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L31" t="n">
-        <v>0.002720421089964731</v>
+        <v>0.002155886440584842</v>
       </c>
       <c r="M31" t="n">
-        <v>11.52798997172911</v>
+        <v>11.48936122770637</v>
       </c>
       <c r="N31" t="n">
-        <v>227.0607050628112</v>
+        <v>225.4983948537058</v>
       </c>
       <c r="O31" t="n">
-        <v>15.0685336069178</v>
+        <v>15.01660397206059</v>
       </c>
       <c r="P31" t="n">
-        <v>281.6969811764866</v>
+        <v>281.799706989464</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -16799,28 +16929,28 @@
         <v>0.0701</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.06509662458942525</v>
+        <v>-0.0804661380272048</v>
       </c>
       <c r="J32" t="n">
+        <v>110</v>
+      </c>
+      <c r="K32" t="n">
         <v>109</v>
       </c>
-      <c r="K32" t="n">
-        <v>108</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.001052031653488772</v>
+        <v>0.001628003304715242</v>
       </c>
       <c r="M32" t="n">
-        <v>12.78785567076588</v>
+        <v>12.75058091694495</v>
       </c>
       <c r="N32" t="n">
-        <v>264.031743446551</v>
+        <v>262.5314065215376</v>
       </c>
       <c r="O32" t="n">
-        <v>16.24905361695108</v>
+        <v>16.20282094332767</v>
       </c>
       <c r="P32" t="n">
-        <v>286.4283531332816</v>
+        <v>286.5718516050915</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -16877,28 +17007,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4140640981430875</v>
+        <v>-0.4314631363451236</v>
       </c>
       <c r="J33" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K33" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04443834999624841</v>
+        <v>0.04862235340038712</v>
       </c>
       <c r="M33" t="n">
-        <v>12.14341247240303</v>
+        <v>12.11706330976274</v>
       </c>
       <c r="N33" t="n">
-        <v>236.0362701564014</v>
+        <v>234.9948252439392</v>
       </c>
       <c r="O33" t="n">
-        <v>15.36347194342481</v>
+        <v>15.32954093389425</v>
       </c>
       <c r="P33" t="n">
-        <v>303.6095700458138</v>
+        <v>303.7756932061034</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -16955,28 +17085,28 @@
         <v>0.0675</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1565077155246846</v>
+        <v>-0.1786901321551456</v>
       </c>
       <c r="J34" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K34" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L34" t="n">
-        <v>0.006931865350582211</v>
+        <v>0.009093579898077353</v>
       </c>
       <c r="M34" t="n">
-        <v>12.28875539182051</v>
+        <v>12.29050529741277</v>
       </c>
       <c r="N34" t="n">
-        <v>231.3684026083594</v>
+        <v>231.1475003997032</v>
       </c>
       <c r="O34" t="n">
-        <v>15.21079888133294</v>
+        <v>15.20353578611578</v>
       </c>
       <c r="P34" t="n">
-        <v>311.0186359683133</v>
+        <v>311.2251160461076</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -17033,28 +17163,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1032955593354671</v>
+        <v>-0.118813179277325</v>
       </c>
       <c r="J35" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K35" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0027078818533397</v>
+        <v>0.003626560795705003</v>
       </c>
       <c r="M35" t="n">
-        <v>13.42416841811261</v>
+        <v>13.3775491497401</v>
       </c>
       <c r="N35" t="n">
-        <v>258.1422035335192</v>
+        <v>256.6476475076806</v>
       </c>
       <c r="O35" t="n">
-        <v>16.06680439706413</v>
+        <v>16.02022620026573</v>
       </c>
       <c r="P35" t="n">
-        <v>318.4802256457657</v>
+        <v>318.626035026546</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -17111,28 +17241,28 @@
         <v>0.0713</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1388767360419329</v>
+        <v>-0.1477690620713878</v>
       </c>
       <c r="J36" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K36" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L36" t="n">
-        <v>0.005952839840068669</v>
+        <v>0.006838841414791408</v>
       </c>
       <c r="M36" t="n">
-        <v>12.83353584039688</v>
+        <v>12.75574374025604</v>
       </c>
       <c r="N36" t="n">
-        <v>214.2915539747086</v>
+        <v>212.5406948811296</v>
       </c>
       <c r="O36" t="n">
-        <v>14.63870055622112</v>
+        <v>14.57877549320003</v>
       </c>
       <c r="P36" t="n">
-        <v>335.0589633594651</v>
+        <v>335.1417361223348</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -17189,28 +17319,28 @@
         <v>0.0823</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.01345603156767761</v>
+        <v>-0.01620723118171978</v>
       </c>
       <c r="J37" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K37" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L37" t="n">
-        <v>6.2382578163378e-05</v>
+        <v>9.203171710481239e-05</v>
       </c>
       <c r="M37" t="n">
-        <v>11.88835762434604</v>
+        <v>11.789902050102</v>
       </c>
       <c r="N37" t="n">
-        <v>193.1109247125734</v>
+        <v>191.2837280493432</v>
       </c>
       <c r="O37" t="n">
-        <v>13.89643568374903</v>
+        <v>13.83053607237779</v>
       </c>
       <c r="P37" t="n">
-        <v>329.2698648093587</v>
+        <v>329.29547390112</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -17248,7 +17378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL110"/>
+  <dimension ref="A1:AL111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37279,6 +37409,198 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>-34.48236461818888,173.00279540302645</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>-34.48302952761015,173.0023995418302</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>-34.48372836180873,173.0020830298592</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-34.484372903132844,173.00163955990683</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-34.48515290338523,173.0014697614778</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-34.485909740902194,173.0013313779296</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-34.48666189669594,173.00130272426966</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-34.48740264336078,173.00129654307457</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>-34.48814483139888,173.00125492842733</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>-34.48888484942607,173.00132720346213</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>-34.4895929336666,173.00167409966312</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>-34.490364056664276,173.0014884412353</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>-34.49110173723763,173.0015769036898</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>-34.49183891198347,173.00166946009685</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>-34.49258731767337,173.00166988442606</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>-34.49332503167596,173.0017579128971</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>-34.49406085982195,173.00186135000396</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>-34.494803584618,173.0019325741461</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>-34.49553559889234,173.00210172727967</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>-34.49627011766438,173.00223131199792</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>-34.497009011776775,173.00231814581701</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>-34.49775061719937,173.00238575911166</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>-34.498494547007105,173.00244734017147</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>-34.49923901897963,173.00257593905243</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>-34.499990932788954,173.00265979247078</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>-34.50072954023723,173.00276260398263</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>-34.50146068497481,173.00290871307186</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>-34.50217992236312,173.00312392980072</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>-34.50290137567429,173.00332624248213</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>-34.503622661543176,173.0034832485385</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>-34.50429792486823,173.00361508769848</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>-34.50498465508992,173.00374505396957</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>-34.5057166208212,173.00392385933011</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>-34.5064470750071,173.00412951271582</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>-34.507225139309874,173.0044171028101</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>-34.507959458450564,173.0047707666133</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0007/nzd0007.xlsx
+++ b/data/nzd0007/nzd0007.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL111"/>
+  <dimension ref="A1:AL112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13277,6 +13277,126 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>293.96</v>
+      </c>
+      <c r="C112" t="n">
+        <v>306.4</v>
+      </c>
+      <c r="D112" t="n">
+        <v>328.22</v>
+      </c>
+      <c r="E112" t="n">
+        <v>338.84</v>
+      </c>
+      <c r="F112" t="n">
+        <v>349.98</v>
+      </c>
+      <c r="G112" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="H112" t="n">
+        <v>368.99</v>
+      </c>
+      <c r="I112" t="n">
+        <v>349.75</v>
+      </c>
+      <c r="J112" t="n">
+        <v>348.09</v>
+      </c>
+      <c r="K112" t="n">
+        <v>358.43</v>
+      </c>
+      <c r="L112" t="n">
+        <v>375.29</v>
+      </c>
+      <c r="M112" t="n">
+        <v>341.68</v>
+      </c>
+      <c r="N112" t="n">
+        <v>350.16</v>
+      </c>
+      <c r="O112" t="n">
+        <v>346.22</v>
+      </c>
+      <c r="P112" t="n">
+        <v>331.53</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>326.34</v>
+      </c>
+      <c r="R112" t="n">
+        <v>324.98</v>
+      </c>
+      <c r="S112" t="n">
+        <v>319.46</v>
+      </c>
+      <c r="T112" t="n">
+        <v>323.77</v>
+      </c>
+      <c r="U112" t="n">
+        <v>320.55</v>
+      </c>
+      <c r="V112" t="n">
+        <v>317.02</v>
+      </c>
+      <c r="W112" t="n">
+        <v>307.22</v>
+      </c>
+      <c r="X112" t="n">
+        <v>298.91</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>296.55</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>288.37</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>276.38</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>272.34</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>275.73</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>276.94</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>271.46</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>269.66</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>275.74</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>286.84</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>300.46</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>319.51</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>318.76</v>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13288,7 +13408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14421,6 +14541,16 @@
       </c>
       <c r="B113" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -14589,28 +14719,28 @@
         <v>0.0633</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06417756858707477</v>
+        <v>-0.08621181860058018</v>
       </c>
       <c r="J2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001223006007027738</v>
+        <v>0.002222168411876502</v>
       </c>
       <c r="M2" t="n">
-        <v>12.8005486257261</v>
+        <v>12.77642816165854</v>
       </c>
       <c r="N2" t="n">
-        <v>236.2204115689058</v>
+        <v>235.6733203838207</v>
       </c>
       <c r="O2" t="n">
-        <v>15.36946360706534</v>
+        <v>15.35165529784397</v>
       </c>
       <c r="P2" t="n">
-        <v>309.499416115075</v>
+        <v>309.7039450717497</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14667,28 +14797,28 @@
         <v>0.047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08720585521628048</v>
+        <v>0.09250981707476563</v>
       </c>
       <c r="J3" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001893042053264682</v>
+        <v>0.002162938818186078</v>
       </c>
       <c r="M3" t="n">
-        <v>13.02351504609312</v>
+        <v>12.91585682578489</v>
       </c>
       <c r="N3" t="n">
-        <v>274.7818628531152</v>
+        <v>271.9159090879706</v>
       </c>
       <c r="O3" t="n">
-        <v>16.57654556453531</v>
+        <v>16.48987292516139</v>
       </c>
       <c r="P3" t="n">
-        <v>300.7176509710189</v>
+        <v>300.6670296678831</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14745,28 +14875,28 @@
         <v>0.0373</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2505743904568127</v>
+        <v>0.2908104229450301</v>
       </c>
       <c r="J4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01285916633327189</v>
+        <v>0.01715000207866879</v>
       </c>
       <c r="M4" t="n">
-        <v>14.53963059215096</v>
+        <v>14.68621202118937</v>
       </c>
       <c r="N4" t="n">
-        <v>321.8089511461866</v>
+        <v>325.1168618331959</v>
       </c>
       <c r="O4" t="n">
-        <v>17.93903428688921</v>
+        <v>18.03099725010228</v>
       </c>
       <c r="P4" t="n">
-        <v>296.3080201692172</v>
+        <v>295.9138605844201</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14823,28 +14953,28 @@
         <v>0.0321</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2025066448973497</v>
+        <v>-0.1520101431484293</v>
       </c>
       <c r="J5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01004656232438694</v>
+        <v>0.005563790811800473</v>
       </c>
       <c r="M5" t="n">
-        <v>13.64988745076612</v>
+        <v>13.79008898279909</v>
       </c>
       <c r="N5" t="n">
-        <v>290.7948025246171</v>
+        <v>298.8603909620244</v>
       </c>
       <c r="O5" t="n">
-        <v>17.05270660407365</v>
+        <v>17.28757909488846</v>
       </c>
       <c r="P5" t="n">
-        <v>311.4851125340024</v>
+        <v>311.0276268480453</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14901,28 +15031,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06500983572502822</v>
+        <v>0.0946316346560797</v>
       </c>
       <c r="J6" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K6" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008307961321309953</v>
+        <v>0.001769156803833605</v>
       </c>
       <c r="M6" t="n">
-        <v>14.16524326521627</v>
+        <v>14.20931208106243</v>
       </c>
       <c r="N6" t="n">
-        <v>332.9151654122036</v>
+        <v>332.8985337826903</v>
       </c>
       <c r="O6" t="n">
-        <v>18.24596298944519</v>
+        <v>18.24550722185301</v>
       </c>
       <c r="P6" t="n">
-        <v>329.8125676470063</v>
+        <v>329.5219864043879</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14979,28 +15109,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07897480385422478</v>
+        <v>-0.03766694106814827</v>
       </c>
       <c r="J7" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009625258910629375</v>
+        <v>0.0002190866888235332</v>
       </c>
       <c r="M7" t="n">
-        <v>15.86803485849711</v>
+        <v>15.90747543248011</v>
       </c>
       <c r="N7" t="n">
-        <v>389.5328753643378</v>
+        <v>391.5862203468249</v>
       </c>
       <c r="O7" t="n">
-        <v>19.73658722688241</v>
+        <v>19.78853760000533</v>
       </c>
       <c r="P7" t="n">
-        <v>349.0491511459758</v>
+        <v>348.611337432606</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15057,28 +15187,28 @@
         <v>0.1955</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1405355742235672</v>
+        <v>0.1735803463682779</v>
       </c>
       <c r="J8" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003668670336343327</v>
+        <v>0.005611237616825027</v>
       </c>
       <c r="M8" t="n">
-        <v>14.06052377147866</v>
+        <v>14.0354205176308</v>
       </c>
       <c r="N8" t="n">
-        <v>321.9135747320866</v>
+        <v>322.2023186032469</v>
       </c>
       <c r="O8" t="n">
-        <v>17.941950137376</v>
+        <v>17.94999494716494</v>
       </c>
       <c r="P8" t="n">
-        <v>346.3702983257932</v>
+        <v>346.0200357247234</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15135,28 +15265,28 @@
         <v>0.1138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03300023012988491</v>
+        <v>0.02556605374746826</v>
       </c>
       <c r="J9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K9" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001808298018705079</v>
+        <v>0.0001103456307643969</v>
       </c>
       <c r="M9" t="n">
-        <v>14.45488248997447</v>
+        <v>14.3645284189119</v>
       </c>
       <c r="N9" t="n">
-        <v>381.4580126980066</v>
+        <v>377.5167991536517</v>
       </c>
       <c r="O9" t="n">
-        <v>19.53095012276685</v>
+        <v>19.42979153654644</v>
       </c>
       <c r="P9" t="n">
-        <v>353.2830013331564</v>
+        <v>353.357918096527</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15213,28 +15343,28 @@
         <v>0.0704</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3250473536507549</v>
+        <v>0.2972017824620252</v>
       </c>
       <c r="J10" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01797608425927266</v>
+        <v>0.01521685504799519</v>
       </c>
       <c r="M10" t="n">
-        <v>15.9072224422954</v>
+        <v>15.95788793041329</v>
       </c>
       <c r="N10" t="n">
-        <v>393.8091772119072</v>
+        <v>392.5109240551897</v>
       </c>
       <c r="O10" t="n">
-        <v>19.84462590254367</v>
+        <v>19.81188845252238</v>
       </c>
       <c r="P10" t="n">
-        <v>356.345258755496</v>
+        <v>356.6080433143795</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15291,28 +15421,28 @@
         <v>0.0929</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5053555069569945</v>
+        <v>0.4859604454606019</v>
       </c>
       <c r="J11" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K11" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0353214977459565</v>
+        <v>0.03316108622188607</v>
       </c>
       <c r="M11" t="n">
-        <v>16.86136883824032</v>
+        <v>16.79611213817603</v>
       </c>
       <c r="N11" t="n">
-        <v>476.331467221567</v>
+        <v>473.1453030448844</v>
       </c>
       <c r="O11" t="n">
-        <v>21.82501929487273</v>
+        <v>21.75190343498436</v>
       </c>
       <c r="P11" t="n">
-        <v>357.8008898550318</v>
+        <v>357.9828163958938</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15369,28 +15499,28 @@
         <v>0.0535</v>
       </c>
       <c r="I12" t="n">
-        <v>0.46799894887752</v>
+        <v>0.4772047051157694</v>
       </c>
       <c r="J12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03712422166357399</v>
+        <v>0.03911444669355657</v>
       </c>
       <c r="M12" t="n">
-        <v>15.87521958718525</v>
+        <v>15.78784190232631</v>
       </c>
       <c r="N12" t="n">
-        <v>387.9488223015954</v>
+        <v>384.4246459815484</v>
       </c>
       <c r="O12" t="n">
-        <v>19.69641648375652</v>
+        <v>19.60675001068633</v>
       </c>
       <c r="P12" t="n">
-        <v>356.8881796612859</v>
+        <v>356.8018292576661</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15447,28 +15577,28 @@
         <v>0.0434</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2179970397007688</v>
+        <v>0.1877714446752735</v>
       </c>
       <c r="J13" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L13" t="n">
-        <v>0.009135045842952438</v>
+        <v>0.006834591696378345</v>
       </c>
       <c r="M13" t="n">
-        <v>14.58219475656934</v>
+        <v>14.57782705824916</v>
       </c>
       <c r="N13" t="n">
-        <v>360.4496500520449</v>
+        <v>360.7678185629505</v>
       </c>
       <c r="O13" t="n">
-        <v>18.98551158257383</v>
+        <v>18.993888979431</v>
       </c>
       <c r="P13" t="n">
-        <v>356.0156095462981</v>
+        <v>356.2891779105348</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15525,28 +15655,28 @@
         <v>0.0688</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1459303983734409</v>
+        <v>0.1374304001189995</v>
       </c>
       <c r="J14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005407960631493625</v>
+        <v>0.00487478926832885</v>
       </c>
       <c r="M14" t="n">
-        <v>12.32982267698232</v>
+        <v>12.2478509869468</v>
       </c>
       <c r="N14" t="n">
-        <v>272.1420578711435</v>
+        <v>269.8237558013907</v>
       </c>
       <c r="O14" t="n">
-        <v>16.49672870211375</v>
+        <v>16.42631290951779</v>
       </c>
       <c r="P14" t="n">
-        <v>351.9473825319869</v>
+        <v>352.0244786864075</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15603,28 +15733,28 @@
         <v>0.0736</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09983617371998973</v>
+        <v>0.08964056458967906</v>
       </c>
       <c r="J15" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003464406189187641</v>
+        <v>0.002836174100548261</v>
       </c>
       <c r="M15" t="n">
-        <v>10.73293848991636</v>
+        <v>10.6719027807997</v>
       </c>
       <c r="N15" t="n">
-        <v>197.7934862175143</v>
+        <v>196.3337955157558</v>
       </c>
       <c r="O15" t="n">
-        <v>14.06390721732457</v>
+        <v>14.01191619714291</v>
       </c>
       <c r="P15" t="n">
-        <v>350.3444990769104</v>
+        <v>350.4372372796224</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15681,28 +15811,28 @@
         <v>0.0673</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09012236365655457</v>
+        <v>0.06572605432878054</v>
       </c>
       <c r="J16" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K16" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002990683697169261</v>
+        <v>0.001598349024901746</v>
       </c>
       <c r="M16" t="n">
-        <v>10.54905856870271</v>
+        <v>10.58853670963136</v>
       </c>
       <c r="N16" t="n">
-        <v>185.8975445971609</v>
+        <v>186.5956545313301</v>
       </c>
       <c r="O16" t="n">
-        <v>13.63442498227046</v>
+        <v>13.66000199602219</v>
       </c>
       <c r="P16" t="n">
-        <v>345.4827336306223</v>
+        <v>345.7059697155004</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -15759,28 +15889,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01706276794688672</v>
+        <v>-0.009645151127548504</v>
       </c>
       <c r="J17" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K17" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L17" t="n">
-        <v>9.883761493278964e-05</v>
+        <v>3.166069683624428e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>11.04284503233575</v>
+        <v>11.08757409402042</v>
       </c>
       <c r="N17" t="n">
-        <v>194.7736873997084</v>
+        <v>195.7877663658679</v>
       </c>
       <c r="O17" t="n">
-        <v>13.95613440031689</v>
+        <v>13.99241817434956</v>
       </c>
       <c r="P17" t="n">
-        <v>343.5930513264728</v>
+        <v>343.8434570464646</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -15837,28 +15967,28 @@
         <v>0.0665</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05066628529125192</v>
+        <v>-0.06724619074399892</v>
       </c>
       <c r="J18" t="n">
+        <v>111</v>
+      </c>
+      <c r="K18" t="n">
         <v>110</v>
       </c>
-      <c r="K18" t="n">
-        <v>109</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.0008010567358921472</v>
+        <v>0.001426056583662683</v>
       </c>
       <c r="M18" t="n">
-        <v>11.76622891794796</v>
+        <v>11.76435575860647</v>
       </c>
       <c r="N18" t="n">
-        <v>217.49752849892</v>
+        <v>216.6563477162664</v>
       </c>
       <c r="O18" t="n">
-        <v>14.74779741178051</v>
+        <v>14.71925092238958</v>
       </c>
       <c r="P18" t="n">
-        <v>337.6376406381205</v>
+        <v>337.7899355893086</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -15915,28 +16045,28 @@
         <v>0.0692</v>
       </c>
       <c r="I19" t="n">
-        <v>0.02891386267717608</v>
+        <v>0.007583013467239469</v>
       </c>
       <c r="J19" t="n">
+        <v>111</v>
+      </c>
+      <c r="K19" t="n">
         <v>110</v>
       </c>
-      <c r="K19" t="n">
-        <v>109</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.0002498150621053075</v>
+        <v>1.73308992063026e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>11.67797522225657</v>
+        <v>11.70303630006491</v>
       </c>
       <c r="N19" t="n">
-        <v>220.2512630917714</v>
+        <v>220.05294720858</v>
       </c>
       <c r="O19" t="n">
-        <v>14.84086463423784</v>
+        <v>14.83418171685179</v>
       </c>
       <c r="P19" t="n">
-        <v>332.967007577334</v>
+        <v>333.1680981407598</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -15993,28 +16123,28 @@
         <v>0.0704</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09503910869126168</v>
+        <v>0.08825424814433463</v>
       </c>
       <c r="J20" t="n">
+        <v>111</v>
+      </c>
+      <c r="K20" t="n">
         <v>110</v>
       </c>
-      <c r="K20" t="n">
-        <v>109</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.002396583722348411</v>
+        <v>0.002100245700598746</v>
       </c>
       <c r="M20" t="n">
-        <v>13.02391143174509</v>
+        <v>12.94539114631502</v>
       </c>
       <c r="N20" t="n">
-        <v>247.5160342209701</v>
+        <v>245.4484017346565</v>
       </c>
       <c r="O20" t="n">
-        <v>15.73264231529371</v>
+        <v>15.66679296265373</v>
       </c>
       <c r="P20" t="n">
-        <v>325.8002385281889</v>
+        <v>325.8642008869642</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -16071,28 +16201,28 @@
         <v>0.0697</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2812303153936411</v>
+        <v>0.2753023401692252</v>
       </c>
       <c r="J21" t="n">
+        <v>111</v>
+      </c>
+      <c r="K21" t="n">
         <v>110</v>
       </c>
-      <c r="K21" t="n">
-        <v>109</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02073444242613376</v>
+        <v>0.02020137982057335</v>
       </c>
       <c r="M21" t="n">
-        <v>12.88278163838243</v>
+        <v>12.79806177661846</v>
       </c>
       <c r="N21" t="n">
-        <v>245.9040563228538</v>
+        <v>243.8078887227254</v>
       </c>
       <c r="O21" t="n">
-        <v>15.68132827036198</v>
+        <v>15.61434880879524</v>
       </c>
       <c r="P21" t="n">
-        <v>317.0908316296705</v>
+        <v>317.1467159437979</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -16149,28 +16279,28 @@
         <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2878685937372238</v>
+        <v>0.2850559914536656</v>
       </c>
       <c r="J22" t="n">
+        <v>111</v>
+      </c>
+      <c r="K22" t="n">
         <v>110</v>
       </c>
-      <c r="K22" t="n">
-        <v>109</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.02434793956282333</v>
+        <v>0.02427223941361867</v>
       </c>
       <c r="M22" t="n">
-        <v>12.09077049588617</v>
+        <v>11.99801060013715</v>
       </c>
       <c r="N22" t="n">
-        <v>218.6022509780495</v>
+        <v>216.6463216300284</v>
       </c>
       <c r="O22" t="n">
-        <v>14.78520378547585</v>
+        <v>14.71891034112337</v>
       </c>
       <c r="P22" t="n">
-        <v>311.2934800926459</v>
+        <v>311.3199951072301</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -16227,28 +16357,28 @@
         <v>0.0565</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1176917584535438</v>
+        <v>0.1118717384619325</v>
       </c>
       <c r="J23" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K23" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004400577365030856</v>
+        <v>0.004041924872662861</v>
       </c>
       <c r="M23" t="n">
-        <v>11.36581838626511</v>
+        <v>11.29470655967286</v>
       </c>
       <c r="N23" t="n">
-        <v>209.8753849645623</v>
+        <v>208.0855696400501</v>
       </c>
       <c r="O23" t="n">
-        <v>14.48707648093853</v>
+        <v>14.42517139031804</v>
       </c>
       <c r="P23" t="n">
-        <v>308.0105605863842</v>
+        <v>308.0646026809142</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -16305,28 +16435,28 @@
         <v>0.061</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1555348529095272</v>
+        <v>0.1441303287572174</v>
       </c>
       <c r="J24" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K24" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L24" t="n">
-        <v>0.005726443312051299</v>
+        <v>0.004995815356093281</v>
       </c>
       <c r="M24" t="n">
-        <v>13.29108363977522</v>
+        <v>13.22579193923077</v>
       </c>
       <c r="N24" t="n">
-        <v>268.9001853555052</v>
+        <v>266.8787755677549</v>
       </c>
       <c r="O24" t="n">
-        <v>16.39817628138889</v>
+        <v>16.33642480984609</v>
       </c>
       <c r="P24" t="n">
-        <v>302.1508527402226</v>
+        <v>302.2612702014407</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -16383,28 +16513,28 @@
         <v>0.0519</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1218461695905215</v>
+        <v>0.115772088390577</v>
       </c>
       <c r="J25" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K25" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003639537232209222</v>
+        <v>0.003340942867626207</v>
       </c>
       <c r="M25" t="n">
-        <v>13.10776069284124</v>
+        <v>13.02294910793557</v>
       </c>
       <c r="N25" t="n">
-        <v>263.4408400215042</v>
+        <v>261.14287187378</v>
       </c>
       <c r="O25" t="n">
-        <v>16.23086072953324</v>
+        <v>16.15991558993363</v>
       </c>
       <c r="P25" t="n">
-        <v>297.2914356904808</v>
+        <v>297.3494819622301</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -16461,28 +16591,28 @@
         <v>0.0309</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5091724401374191</v>
+        <v>0.4966768445206437</v>
       </c>
       <c r="J26" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K26" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03659905810743969</v>
+        <v>0.03541749687165419</v>
       </c>
       <c r="M26" t="n">
-        <v>17.30318924802332</v>
+        <v>17.20951350101009</v>
       </c>
       <c r="N26" t="n">
-        <v>440.6471408847539</v>
+        <v>437.0822817395879</v>
       </c>
       <c r="O26" t="n">
-        <v>20.99159691125842</v>
+        <v>20.90651290243277</v>
       </c>
       <c r="P26" t="n">
-        <v>282.9521587237729</v>
+        <v>283.0723710811205</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -16539,28 +16669,28 @@
         <v>0.0427</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2466512453018694</v>
+        <v>0.225150659121966</v>
       </c>
       <c r="J27" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K27" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01049016030634931</v>
+        <v>0.008860738748024954</v>
       </c>
       <c r="M27" t="n">
-        <v>15.37512423115409</v>
+        <v>15.37816556163191</v>
       </c>
       <c r="N27" t="n">
-        <v>378.2410415187089</v>
+        <v>376.4859094978108</v>
       </c>
       <c r="O27" t="n">
-        <v>19.44842002628257</v>
+        <v>19.40324481878768</v>
       </c>
       <c r="P27" t="n">
-        <v>283.9095370181527</v>
+        <v>284.1133382627952</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -16617,28 +16747,28 @@
         <v>0.0517</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2061643653635009</v>
+        <v>-0.2265059661296935</v>
       </c>
       <c r="J28" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K28" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01075353859225647</v>
+        <v>0.01308947502569557</v>
       </c>
       <c r="M28" t="n">
-        <v>12.67763558867127</v>
+        <v>12.69818435109086</v>
       </c>
       <c r="N28" t="n">
-        <v>248.1572913357633</v>
+        <v>247.3813845785754</v>
       </c>
       <c r="O28" t="n">
-        <v>15.75300896133063</v>
+        <v>15.7283624252042</v>
       </c>
       <c r="P28" t="n">
-        <v>290.8109735459403</v>
+        <v>291.0091510977297</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -16695,28 +16825,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1112630403669867</v>
+        <v>-0.1233862278229666</v>
       </c>
       <c r="J29" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K29" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L29" t="n">
-        <v>0.003449677831846132</v>
+        <v>0.004298384665823329</v>
       </c>
       <c r="M29" t="n">
-        <v>12.70321804338005</v>
+        <v>12.66166334875419</v>
       </c>
       <c r="N29" t="n">
-        <v>240.9351209074662</v>
+        <v>239.3649709350468</v>
       </c>
       <c r="O29" t="n">
-        <v>15.52208494073738</v>
+        <v>15.47142433439943</v>
       </c>
       <c r="P29" t="n">
-        <v>286.9357086925357</v>
+        <v>287.0475344432562</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -16773,28 +16903,28 @@
         <v>0.0708</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1127094929228719</v>
+        <v>0.09948276340008148</v>
       </c>
       <c r="J30" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K30" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L30" t="n">
-        <v>0.004174459826171373</v>
+        <v>0.003297477375047819</v>
       </c>
       <c r="M30" t="n">
-        <v>11.25423187068384</v>
+        <v>11.23565651861254</v>
       </c>
       <c r="N30" t="n">
-        <v>204.1651138661713</v>
+        <v>203.0405127952114</v>
       </c>
       <c r="O30" t="n">
-        <v>14.28863582943352</v>
+        <v>14.24922849824549</v>
       </c>
       <c r="P30" t="n">
-        <v>282.9802024362338</v>
+        <v>283.1022073927547</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -16851,28 +16981,28 @@
         <v>0.0684</v>
       </c>
       <c r="I31" t="n">
-        <v>0.08503829296390146</v>
+        <v>0.0665890241499089</v>
       </c>
       <c r="J31" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K31" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L31" t="n">
-        <v>0.002155886440584842</v>
+        <v>0.001336658380814537</v>
       </c>
       <c r="M31" t="n">
-        <v>11.48936122770637</v>
+        <v>11.4929231936569</v>
       </c>
       <c r="N31" t="n">
-        <v>225.4983948537058</v>
+        <v>224.8574447472197</v>
       </c>
       <c r="O31" t="n">
-        <v>15.01660397206059</v>
+        <v>14.99524740533546</v>
       </c>
       <c r="P31" t="n">
-        <v>281.799706989464</v>
+        <v>281.9698852815063</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -16929,28 +17059,28 @@
         <v>0.0701</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0804661380272048</v>
+        <v>-0.1024976866341956</v>
       </c>
       <c r="J32" t="n">
+        <v>111</v>
+      </c>
+      <c r="K32" t="n">
         <v>110</v>
       </c>
-      <c r="K32" t="n">
-        <v>109</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.001628003304715242</v>
+        <v>0.002662994354905579</v>
       </c>
       <c r="M32" t="n">
-        <v>12.75058091694495</v>
+        <v>12.74727823592835</v>
       </c>
       <c r="N32" t="n">
-        <v>262.5314065215376</v>
+        <v>262.0824923307338</v>
       </c>
       <c r="O32" t="n">
-        <v>16.20282094332767</v>
+        <v>16.18896205229766</v>
       </c>
       <c r="P32" t="n">
-        <v>286.5718516050915</v>
+        <v>286.778878389585</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -17007,28 +17137,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4314631363451236</v>
+        <v>-0.4567716256882633</v>
       </c>
       <c r="J33" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K33" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04862235340038712</v>
+        <v>0.05448883439094887</v>
       </c>
       <c r="M33" t="n">
-        <v>12.11706330976274</v>
+        <v>12.13073026523069</v>
       </c>
       <c r="N33" t="n">
-        <v>234.9948252439392</v>
+        <v>235.3150570545863</v>
       </c>
       <c r="O33" t="n">
-        <v>15.32954093389425</v>
+        <v>15.33998230294241</v>
       </c>
       <c r="P33" t="n">
-        <v>303.7756932061034</v>
+        <v>304.0188622757941</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -17085,28 +17215,28 @@
         <v>0.0675</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1786901321551456</v>
+        <v>-0.2081027187325865</v>
       </c>
       <c r="J34" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K34" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L34" t="n">
-        <v>0.009093579898077353</v>
+        <v>0.01231365030052123</v>
       </c>
       <c r="M34" t="n">
-        <v>12.29050529741277</v>
+        <v>12.3280967844786</v>
       </c>
       <c r="N34" t="n">
-        <v>231.1475003997032</v>
+        <v>232.4828417563913</v>
       </c>
       <c r="O34" t="n">
-        <v>15.20353578611578</v>
+        <v>15.24738803062319</v>
       </c>
       <c r="P34" t="n">
-        <v>311.2251160461076</v>
+        <v>311.5006781696468</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -17163,28 +17293,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.118813179277325</v>
+        <v>-0.141499137562183</v>
       </c>
       <c r="J35" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K35" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L35" t="n">
-        <v>0.003626560795705003</v>
+        <v>0.005179418631815369</v>
       </c>
       <c r="M35" t="n">
-        <v>13.3775491497401</v>
+        <v>13.37020723193779</v>
       </c>
       <c r="N35" t="n">
-        <v>256.6476475076806</v>
+        <v>256.3055981599721</v>
       </c>
       <c r="O35" t="n">
-        <v>16.02022620026573</v>
+        <v>16.00954709415517</v>
       </c>
       <c r="P35" t="n">
-        <v>318.626035026546</v>
+        <v>318.8406070959985</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -17241,28 +17371,28 @@
         <v>0.0713</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1477690620713878</v>
+        <v>-0.1656107187349146</v>
       </c>
       <c r="J36" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K36" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L36" t="n">
-        <v>0.006838841414791408</v>
+        <v>0.008666100034132707</v>
       </c>
       <c r="M36" t="n">
-        <v>12.75574374025604</v>
+        <v>12.72391814943957</v>
       </c>
       <c r="N36" t="n">
-        <v>212.5406948811296</v>
+        <v>211.7921518335556</v>
       </c>
       <c r="O36" t="n">
-        <v>14.57877549320003</v>
+        <v>14.55308049292505</v>
       </c>
       <c r="P36" t="n">
-        <v>335.1417361223348</v>
+        <v>335.3089281828937</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -17319,28 +17449,28 @@
         <v>0.0823</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.01620723118171978</v>
+        <v>-0.03158546882670416</v>
       </c>
       <c r="J37" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K37" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L37" t="n">
-        <v>9.203171710481239e-05</v>
+        <v>0.0003535645814152222</v>
       </c>
       <c r="M37" t="n">
-        <v>11.789902050102</v>
+        <v>11.7645024665123</v>
       </c>
       <c r="N37" t="n">
-        <v>191.2837280493432</v>
+        <v>190.4096887562115</v>
       </c>
       <c r="O37" t="n">
-        <v>13.83053607237779</v>
+        <v>13.79890172282604</v>
       </c>
       <c r="P37" t="n">
-        <v>329.29547390112</v>
+        <v>329.4395815525627</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -17378,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL111"/>
+  <dimension ref="A1:AL112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37601,6 +37731,198 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>-34.482315337458616,173.00268015508487</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>-34.483024520901154,173.00238783309712</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>-34.483772511970066,173.00218628042754</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-34.48447415515903,173.0018763507892</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-34.48518677941775,173.0015659780595</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-34.485935325219074,173.00150176657783</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-34.48666616876197,173.00144486878875</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-34.48739982685144,173.00120283135726</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>-34.488145009853895,173.00115200568297</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>-34.488886854398224,173.00130139523796</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>-34.48960017556423,173.00161472821384</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>-34.4903768316253,173.00138370511348</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>-34.491098162325564,173.00160621281393</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>-34.49183581021263,173.0016948902944</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>-34.49258758053423,173.0016677293051</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>-34.49332685856306,173.00174293467506</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>-34.494061096398255,173.00185941036125</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>-34.49480370869636,173.00193160537216</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>-34.49553269694283,173.0021227864612</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>-34.49626888790249,173.00224000889463</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>-34.497004001622614,173.00235357792747</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>-34.4977486283198,173.0023998247105</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>-34.498492391598575,173.00246236603235</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>-34.49923596085682,173.00259519493838</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>-34.49998512922099,173.00269349254776</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>-34.500731909416665,173.00274884655116</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>-34.50146408264759,173.0028889832529</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>-34.502182603788924,173.00310835911213</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>-34.502905122347656,173.00330448599598</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>-34.503631830671814,173.0034272523115</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>-34.50430349935121,173.0035621363683</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>-34.50498813364302,173.0036829941172</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>-34.50571995324231,173.00386440743458</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>-34.506450230840386,173.0040732122648</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>-34.507237024951735,173.00435166245748</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>-34.50798642639905,173.00468548617252</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
